--- a/cadastro_rede_por_departamento.xlsx
+++ b/cadastro_rede_por_departamento.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="5" t="inlineStr"/>
@@ -636,6 +636,31 @@
       <c r="E13" s="4" t="inlineStr">
         <is>
           <t>infraestrutura</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>dasdasd</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>123123</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>qwe.qwe</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>asd@ggmail.com</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>sistemas</t>
         </is>
       </c>
     </row>
